--- a/data/hex_xlsx/FORTUM.HE.xlsx
+++ b/data/hex_xlsx/FORTUM.HE.xlsx
@@ -23838,7 +23838,9 @@
       <c r="N103" s="17">
         <v>17535.02</v>
       </c>
-      <c r="O103" s="17"/>
+      <c r="O103" s="22">
+        <v>7860.95</v>
+      </c>
       <c r="P103" s="22">
         <v>7156.45</v>
       </c>
